--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/2101-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/2101-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{00D90E76-17DC-415B-B0F6-F48C5D206555}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4296601E-AF6D-48A7-B8AF-49DABCE17771}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{B20E3B87-0781-46BC-A793-ACDBE63F3645}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{698E5F78-47B9-45C7-A5C4-F7D4E03BC35A}"/>
   </bookViews>
   <sheets>
     <sheet name="2101-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1499,28 +1499,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCF9556E-BC23-48C4-B5DA-C4F94B0CC2A5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E459E695-8C92-4C54-B563-46351CF30239}">
   <dimension ref="A1:X55"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="7" width="7.125" customWidth="1"/>
-    <col min="8" max="8" width="6.75" customWidth="1"/>
-    <col min="9" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="14" width="7.125" customWidth="1"/>
-    <col min="15" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.5" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="7" width="6.109375" customWidth="1"/>
+    <col min="8" max="8" width="5.88671875" customWidth="1"/>
+    <col min="9" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="14" width="6.109375" customWidth="1"/>
+    <col min="15" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
@@ -1554,7 +1554,7 @@
       <c r="W1" s="29"/>
       <c r="X1" s="21"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="22" t="s">
         <v>1</v>
       </c>
@@ -1590,7 +1590,7 @@
       <c r="W2" s="31"/>
       <c r="X2" s="32"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="22" t="s">
         <v>2</v>
       </c>
@@ -1642,7 +1642,7 @@
       </c>
       <c r="X3" s="35"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="24"/>
       <c r="B4" s="25"/>
       <c r="C4" s="7"/>
@@ -1710,7 +1710,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="36">
         <v>2025</v>
       </c>
@@ -1782,7 +1782,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>29</v>
       </c>
@@ -1856,7 +1856,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="38">
         <v>2024</v>
       </c>
@@ -1928,7 +1928,7 @@
         <v>1.68</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="16" t="s">
         <v>29</v>
       </c>
@@ -2002,7 +2002,7 @@
         <v>1.68</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
         <v>29</v>
       </c>
@@ -2076,7 +2076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="36">
         <v>2023</v>
       </c>
@@ -2148,7 +2148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>29</v>
       </c>
@@ -2222,7 +2222,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
         <v>29</v>
       </c>
@@ -2296,7 +2296,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="38">
         <v>2022</v>
       </c>
@@ -2368,7 +2368,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="16" t="s">
         <v>29</v>
       </c>
@@ -2442,7 +2442,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="16" t="s">
         <v>29</v>
       </c>
@@ -2516,7 +2516,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="36">
         <v>2021</v>
       </c>
@@ -2588,7 +2588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
         <v>29</v>
       </c>
@@ -2662,7 +2662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
         <v>29</v>
       </c>
@@ -2736,7 +2736,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="38">
         <v>2020</v>
       </c>
@@ -2808,7 +2808,7 @@
         <v>2.76</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="16" t="s">
         <v>29</v>
       </c>
@@ -2882,7 +2882,7 @@
         <v>1.74</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="16" t="s">
         <v>29</v>
       </c>
@@ -2956,7 +2956,7 @@
         <v>1.02</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="36">
         <v>2019</v>
       </c>
@@ -3028,7 +3028,7 @@
         <v>4.1900000000000004</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="11" t="s">
         <v>29</v>
       </c>
@@ -3102,7 +3102,7 @@
         <v>2.19</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="11" t="s">
         <v>29</v>
       </c>
@@ -3176,7 +3176,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="38">
         <v>2018</v>
       </c>
@@ -3248,7 +3248,7 @@
         <v>0.8</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="36">
         <v>2017</v>
       </c>
@@ -3320,7 +3320,7 @@
         <v>3.13</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="38">
         <v>2016</v>
       </c>
@@ -3392,7 +3392,7 @@
         <v>4.3899999999999997</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="36">
         <v>2015</v>
       </c>
@@ -3464,7 +3464,7 @@
         <v>0.82</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="38">
         <v>2014</v>
       </c>
@@ -3536,7 +3536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="36">
         <v>2013</v>
       </c>
@@ -3608,7 +3608,7 @@
         <v>3.54</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="38">
         <v>2012</v>
       </c>
@@ -3680,7 +3680,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="36">
         <v>2011</v>
       </c>
@@ -3752,7 +3752,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="38">
         <v>2010</v>
       </c>
@@ -3824,7 +3824,7 @@
         <v>2.73</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="36">
         <v>2009</v>
       </c>
@@ -3896,7 +3896,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="38">
         <v>2008</v>
       </c>
@@ -3968,7 +3968,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="36">
         <v>2007</v>
       </c>
@@ -4040,7 +4040,7 @@
         <v>30.7</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="38">
         <v>2006</v>
       </c>
@@ -4112,7 +4112,7 @@
         <v>15.8</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="36">
         <v>2005</v>
       </c>
@@ -4184,7 +4184,7 @@
         <v>13.2</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="38">
         <v>2004</v>
       </c>
@@ -4256,7 +4256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="36">
         <v>2003</v>
       </c>
@@ -4328,7 +4328,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="38">
         <v>2002</v>
       </c>
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="36">
         <v>2001</v>
       </c>
@@ -4472,7 +4472,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="38">
         <v>2000</v>
       </c>
@@ -4544,7 +4544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="36">
         <v>1999</v>
       </c>
@@ -4616,7 +4616,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="38">
         <v>1998</v>
       </c>
@@ -4688,7 +4688,7 @@
         <v>6.6</v>
       </c>
     </row>
-    <row r="46" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="36">
         <v>1997</v>
       </c>
@@ -4760,7 +4760,7 @@
         <v>2.4700000000000002</v>
       </c>
     </row>
-    <row r="47" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A47" s="38">
         <v>1996</v>
       </c>
@@ -4832,7 +4832,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="48" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A48" s="36">
         <v>1995</v>
       </c>
@@ -4904,7 +4904,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A49" s="38">
         <v>1994</v>
       </c>
@@ -4976,7 +4976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A50" s="36">
         <v>1993</v>
       </c>
@@ -5048,7 +5048,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A51" s="38">
         <v>1992</v>
       </c>
@@ -5120,7 +5120,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A52" s="36">
         <v>1991</v>
       </c>
@@ -5192,7 +5192,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A53" s="38">
         <v>1990</v>
       </c>
@@ -5264,7 +5264,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A54" s="36">
         <v>1983</v>
       </c>
@@ -5336,7 +5336,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="55" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A55" s="38" t="s">
         <v>53</v>
       </c>
